--- a/光伏配储项目/电价数据/2026/彭洞站.xlsx
+++ b/光伏配储项目/电价数据/2026/彭洞站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5522400000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78366</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.62078</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.58975</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5478099999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.59887</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44099</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43053</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41561</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39432</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42666</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41435</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44617</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49933</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.11135</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.12231</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.13018</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.05873</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.10105</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.15505</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05027</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.50083</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.75346</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14619</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21444</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.23426</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21737</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.1291</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.13809</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.27426</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.53923</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6373099999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.46807</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73272</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.01864</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5326000000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65912</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.36231</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.08975</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.22423</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.9206299999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.11996</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.17156</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.35789</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5732</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.3956</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.11751</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.86694</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79686</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75774</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47985</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47278</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42554</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7098300000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.75953</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8694700000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.91387</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5155599999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5033</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50358</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48574</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46781</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35269</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8941399999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.73291</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.82611</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43994</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37625</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38748</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42738</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50885</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.49486</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.76713</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.98219</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5222599999999999</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9061399999999999</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.8580099999999999</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.70277</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.00979</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.07866</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.05639</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47357</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.54018</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49186</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52973</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.88527</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6411399999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.78569</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.82029</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.17361</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.39437</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.20272</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86937</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.21871</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12006</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.27446</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.05513</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.65939</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9021699999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.01431</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.95631</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.98587</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.80691</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77326</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45141</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.78586</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8025800000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44434</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33464</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50851</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48661</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4518</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41541</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3698</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38947</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42825</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39584</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3955</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44438</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36733</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.23504</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.5406</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.8289299999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.5805800000000001</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.72597</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.8128099999999999</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.54544</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50793</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81633</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.80022</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6651900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.6017899999999999</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49394</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.42456</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43047</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.5174</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.49853</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50812</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.56937</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59348</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5403</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.56029</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.27265</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6175700000000001</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.55211</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45868</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5077900000000001</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6399</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.61251</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.59394</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4993</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43456</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50318</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61191</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.66073</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5631699999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7900199999999999</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.65361</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55857</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.47977</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61381</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45322</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45726</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39782</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.342</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49175</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38845</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35843</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38447</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44922</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39241</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41453</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.68322</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.88274</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.52362</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.24227</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.96308</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.43137</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60282</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.36814</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48144</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.3972</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.5690499999999999</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.53351</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42908</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49596</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44975</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46262</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51877</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.59511</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.46191</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5929800000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.4902</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49861</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41536</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35209</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.3201</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.46121</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45994</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38236</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31517</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31407</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32322</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34692</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.38417</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2051</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22347</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22777</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15955</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.16293</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17226</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.02801</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.3932</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21901</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.16353</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21998</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05833</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.03277</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.00155</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.67688</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29025</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37956</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37265</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39144</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40293</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35701</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34551</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.60246</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.39485</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10264</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04468</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.39589</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0597</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.22906</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.05721</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04359</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.08131000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07958</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36187</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33225</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31488</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45583</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78527</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86291</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18712</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86642</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33088</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03294</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308200000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39992</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44997</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20703</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62188</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41972</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41031</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42797</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32998</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.56457</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.41617</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58721</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.7139</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8772799999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.39742</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55811</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8293400000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.58166</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85729</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.6425</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6584800000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60061</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.1825</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33487</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31905</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30194</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31152</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.29323</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.39494</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.42929</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.39696</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34862</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91438</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.44848</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.44298</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.39422</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3416</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.4701</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31019</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.18482</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33894</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19831</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29907</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28923</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.3152</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.41917</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42162</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4053</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.54745</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8738899999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.46266</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14701</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69125</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7817499999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64237</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.52215</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44354</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49367</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.42175</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.40922</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.47126</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40718</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.40591</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41817</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.41155</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48893</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.53159</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24543</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24898</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16059</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26066</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25409</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28236</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2878</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29734</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34888</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5490499999999999</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43991</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.79762</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.41899</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.44893</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.37345</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.31137</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.29061</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30476</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3349</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.33422</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.24837</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28185</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.25671</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22889</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14253</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.12008</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.26904</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.11847</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13863</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.12941</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.24521</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.12041</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24498</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.12773</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.24376</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11857</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09171</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10157</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.12167</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.18995</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13438</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26207</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32567</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33955</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34929</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.38232</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.42749</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.41542</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39201</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3376</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.50134</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38375</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.44255</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4046</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36892</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29374</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27432</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2864</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25022</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23887</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.43489</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41667</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.42079</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37393</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35451</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41912</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.37308</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35117</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.48254</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33764</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.28474</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.30211</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.66064</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.37078</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51862</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38028</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.40639</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43382</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.21272</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.39123</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.58387</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.51559</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.88579</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43747</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45184</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42636</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45881</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.46024</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41475</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33266</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.68508</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45925</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44021</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42237</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69633</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.68148</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.6274500000000001</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5338200000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5053799999999999</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24331</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37176</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35293</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32218</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42208</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.30784</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.32085</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37468</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.37026</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.34563</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33415</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32911</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27865</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.39497</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.52101</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36346</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.35761</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33835</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33883</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32457</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.50036</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3835</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34362</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65204</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7490599999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.43464</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.27303</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.41152</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33685</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36295</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35388</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.29905</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2644</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.15276</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28921</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.21723</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25608</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.23153</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26509</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28437</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29406</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33329</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33783</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3182</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40339</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6378200000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.59758</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80169</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.71937</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48356</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.44087</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36869</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.35234</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.46332</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.54012</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.48435</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6347999999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.40097</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.39466</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3897</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.39595</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.3832</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.37713</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.42288</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.51702</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.46746</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.50219</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.46334</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.51046</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5469299999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.55012</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.42934</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.36773</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.40245</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.40259</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.423</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.3897</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41343</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6622400000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.48157</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.98023</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.38707</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.38737</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.46577</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.48015</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5142599999999999</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.6383799999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.75276</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.83304</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.58478</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.73314</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.6427</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52111</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.75486</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76622</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61902</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66767</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.46084</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.45574</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44473</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40173</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5159</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41059</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.43337</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42951</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.42402</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38593</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.36183</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38297</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38151</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5295</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38018</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45841</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41744</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.14427</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.21161</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.38296</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39072</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4048</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4271</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.36279</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.38132</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.3873</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.34771</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37098</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.37658</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.34014</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.46878</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.27503</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.26994</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.26671</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.19509</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28356</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2419</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25579</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.10442</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25546</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03629</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.18897</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.21388</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30837</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.24592</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26627</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23871</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27769</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.34823</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.33017</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.28626</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.30074</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.25652</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.25642</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.25855</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.25717</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.28766</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.25234</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.25545</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.25636</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.26099</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17428</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26639</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2224</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01392</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00105</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02019</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0427</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04055</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04855</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02447</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02907</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04938</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00029</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27218</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01867</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03627</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26318</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27946</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.25861</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31141</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34436</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.31588</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.4224</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35322</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36859</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32939</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.74113</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.62197</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.44549</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.41678</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.42052</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.30279</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25777</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.29264</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.28461</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43533</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.70825</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.8573200000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87199</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83551</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37901</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10631</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.21421</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.28167</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.28396</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.25395</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.00244</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.25986</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.00238</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.05470000000000001</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.27477</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25502</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.46885</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.53916</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.80336</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.77871</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.78775</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.36732</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9830800000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.7797799999999999</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.84454</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.8106100000000001</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.84111</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83927</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8436699999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94074</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.77252</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8065</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37359</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.36672</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.47358</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.62415</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.69235</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.5848300000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4941</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.4700299999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38201</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.5032</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.37464</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.4714</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.48462</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.42522</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.46206</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.36757</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.40129</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26389</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31537</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34773</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37703</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43051</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.77604</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41714</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.62503</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.47363</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.42455</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49482</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34545</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43392</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3876</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3586</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.4231</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.58665</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.7851699999999999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.57057</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5286000000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.58499</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.46735</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32496</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40935</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47717</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5903400000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82168</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.63062</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.44161</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5515800000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.66375</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.84121</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.49498</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.74509</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.58609</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47467</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47428</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43364</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43029</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.36627</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.3727200000000001</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.43436</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.24087</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.36209</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.35825</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46267</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.37808</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34014</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34381</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39177</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43566</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.32459</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35634</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37977</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42145</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.52991</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.60376</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.81003</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.7297100000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.7553099999999999</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7381599999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.50526</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.60088</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.6434099999999999</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.49136</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.81776</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.7924500000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.01604</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.89119</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.82338</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.80147</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40544</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38908</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36817</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.36261</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34472</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34025</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34783</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.25881</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30767</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.21738</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.37842</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16764</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.18826</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.21407</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.27453</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.19521</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.24661</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25704</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36213</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.53486</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4245</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.43709</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45205</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45462</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40464</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40533</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40358</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.36901</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.97921</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.41933</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6080399999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5134099999999999</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4685</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37297</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.37384</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3733399999999999</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36876</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.3661</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35921</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.36196</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.54084</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33461</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.42783</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.43866</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.36035</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3475</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42878</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40948</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39767</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35862</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38614</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.38368</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.36515</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.3871</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.38127</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38901</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.4583</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.39861</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42807</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40721</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35534</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36177</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35807</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3218</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17451</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14423</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19642</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.13952</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04159</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1267</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.23536</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16559</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14565</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.21183</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26083</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15256</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.14576</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19558</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14271</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27839</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26033</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34341</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40871</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36612</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.43308</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.39138</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.47227</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39471</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38629</v>
       </c>
     </row>
   </sheetData>
